--- a/e2e-screenshots/return-restore/fixtures/SALES_RETURN_RESTORE_SCENARIO_A.xlsx
+++ b/e2e-screenshots/return-restore/fixtures/SALES_RETURN_RESTORE_SCENARIO_A.xlsx
@@ -8,7 +8,7 @@
     <sheet name="EBAY" sheetId="3" r:id="rId3"/>
     <sheet name="ONBUY" sheetId="4" r:id="rId4"/>
     <sheet name="TEMU" sheetId="5" r:id="rId5"/>
-    <sheet name="Returns" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Detail" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -849,117 +849,111 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Sale Date</v>
+        <v>Return Date</v>
       </c>
       <c r="B1" t="str">
-        <v>Return Date</v>
+        <v>Unit IMEI</v>
       </c>
       <c r="C1" t="str">
+        <v>Model</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Storage</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Colour</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Supplier</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Original Sale Date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Original Sale Price</v>
+      </c>
+      <c r="I1" t="str">
         <v>Marketplace</v>
       </c>
-      <c r="D1" t="str">
-        <v>Order Number</v>
-      </c>
-      <c r="E1" t="str">
-        <v>SKU</v>
-      </c>
-      <c r="F1" t="str">
-        <v>IMEI</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Supplier</v>
-      </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
+        <v>Return Type</v>
+      </c>
+      <c r="K1" t="str">
         <v>Outcome</v>
       </c>
-      <c r="I1" t="str">
-        <v>Return Type</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Return Reason</v>
-      </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
+        <v>Reason</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Comments</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Leg Cost £</v>
+      </c>
+      <c r="O1" t="str">
         <v>Shipping Legs</v>
       </c>
-      <c r="L1" t="str">
+      <c r="P1" t="str">
         <v>Postage Loss £</v>
-      </c>
-      <c r="M1" t="str">
-        <v>BP</v>
-      </c>
-      <c r="N1" t="str">
-        <v>SP</v>
-      </c>
-      <c r="O1" t="str">
-        <v>SP-BP</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Postage</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Comments</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="B2" t="str">
+        <v>350190000001111</v>
+      </c>
+      <c r="C2" t="str">
+        <v>IPHONE 13 128GB</v>
+      </c>
+      <c r="D2" t="str">
+        <v>128GB</v>
+      </c>
+      <c r="E2" t="str">
+        <v>BLACK</v>
+      </c>
+      <c r="F2" t="str">
+        <v>MOBILE WHOLESALE LTD</v>
+      </c>
+      <c r="G2" t="str">
         <v>2026-07-05</v>
       </c>
-      <c r="B2" t="str">
-        <v>2026-07-15</v>
-      </c>
-      <c r="C2" t="str">
+      <c r="H2">
+        <v>450</v>
+      </c>
+      <c r="I2" t="str">
         <v>AMAZON</v>
       </c>
-      <c r="D2" t="str">
-        <v>AMZ-A-1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>IP13-128-BLK</v>
-      </c>
-      <c r="F2" t="str">
-        <v>350190000001111</v>
-      </c>
-      <c r="G2" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
+        <v>Back to Inventory</v>
+      </c>
+      <c r="K2" t="str">
         <v>Refund</v>
       </c>
-      <c r="I2" t="str">
-        <v>Back to Inventory</v>
-      </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>Cx Change of Mind</v>
       </c>
-      <c r="K2">
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2">
+        <v>7.56</v>
+      </c>
+      <c r="O2">
         <v>2</v>
       </c>
-      <c r="L2">
-        <v>12.6</v>
-      </c>
-      <c r="M2">
-        <v>300</v>
-      </c>
-      <c r="N2">
-        <v>450</v>
-      </c>
-      <c r="O2">
-        <v>150</v>
-      </c>
       <c r="P2">
-        <v>6.3</v>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
+        <v>15.12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>